--- a/validation/web/browser-results.xlsx
+++ b/validation/web/browser-results.xlsx
@@ -20,7 +20,13 @@
     <sheet name="可行性与覆盖诊断" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="数据清理记录" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="独立留出指标" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="运行设置" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="预测决策矩阵" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="实测决策矩阵" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="逐代搜索记录" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Pearson相关矩阵" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Spearman相关矩阵" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="相关样本数" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="运行设置" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8090,571 +8096,8805 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B47"/>
+  <dimension ref="A1:AB33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>设置</t>
+          <t>推荐排序</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>值</t>
+          <t>flow_L_min</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>channel_mm</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>channels</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Tmax_K</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>deltaT_K</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>pump_W</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>综合效用</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>理想点距离</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>结果类型</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>最近样本距离</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>约束违反量</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>归一化::Tmax_K</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>方向损失::Tmax_K</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>有效损失::Tmax_K</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>加权平方::Tmax_K</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>归一化::deltaT_K</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>方向损失::deltaT_K</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>有效损失::deltaT_K</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>加权平方::deltaT_K</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>归一化::pump_W</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>方向损失::pump_W</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>有效损失::pump_W</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>加权平方::pump_W</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>S_c</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>复算综合效用</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>效用复算差</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1.997117852294871</v>
+      </c>
+      <c r="C2" t="n">
+        <v>6.870601138731148</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2" t="n">
+        <v>304.7203361692434</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4.929043562077896</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6.529705716121708</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.7262659798652369</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.376906020278626</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>代理模型预测</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>0.09055032942104031</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.2925783928312896</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.2925783928312896</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.2925783928312896</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.02853403865058014</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.3492838469760791</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.3492838469760791</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.3492838469760791</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.04066640191946969</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.4675180452738339</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.4675180452738339</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.4675180452738339</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.07285770755222221</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.376906020278626</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.7262659798652369</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.7262659798652369</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1.941966136701668</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2.489480353150909</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>306.9241496528086</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4.641680095511889</v>
+      </c>
+      <c r="G3" t="n">
+        <v>6.049952988959562</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.7253109833280768</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.3787189536431913</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>代理模型预测</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>0.2065974025237819</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.4352200422529836</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.4352200422529836</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.4352200422529836</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.06313882839289628</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.2446899298952925</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.2446899298952925</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.2446899298952925</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.01995772059738771</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.425434472715751</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.425434472715751</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.425434472715751</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.06033149685830969</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.3787189536431913</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.7253109833280768</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.7253109833280768</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1.711834508575345</v>
+      </c>
+      <c r="C4" t="n">
+        <v>6.870601138731148</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" t="n">
+        <v>305.9351324215983</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5.128741902679338</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5.259982918682832</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.7224710645821655</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.3841384783739967</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>代理模型预测</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>0.2041162252495209</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.3712059819804714</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.3712059819804714</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.3712059819804714</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.0459312936860287</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.4219696059824005</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.4219696059824005</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.4219696059824005</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.05935278279098076</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.3561388525160379</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.3561388525160379</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.3561388525160379</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.04227829409048006</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.3841384783739967</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.7224710645821655</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.7224710645821655</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2.223690061980502</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.058268755756312</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" t="n">
+        <v>305.4942882483896</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4.400056641195904</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7.486670427852006</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.7216996053019188</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.3856180502989964</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>代理模型预测</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0.1010787024524757</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.3426723785365471</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.3426723785365471</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.3426723785365471</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.03914145300396487</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.1567443610047725</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.1567443610047725</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.1567443610047725</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.008189598235598151</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.5514623182326321</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.5514623182326321</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.5514623182326321</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.1013702294768363</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.3856180502989964</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.7216996053019188</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.7216996053019188</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1.51558538902574</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2.893754064681389</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" t="n">
+        <v>308.579283540044</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4.90591651175287</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.301086588957715</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.7133686307089586</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.4017997945973347</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>代理模型预测</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0.2791924386053541</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.5423484491937877</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.5423484491937877</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.5423484491937877</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.09804728011430215</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.3408661145032445</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.3408661145032445</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.3408661145032445</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.03872990267217966</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.2720251393822557</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.2720251393822557</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.2720251393822557</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.02466589215197854</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.4017997945973347</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.7133686307089586</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.7133686307089586</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2.277080057675579</v>
+      </c>
+      <c r="C7" t="n">
+        <v>7.686058237598002</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>303.1928922224544</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4.963246137612201</v>
+      </c>
+      <c r="G7" t="n">
+        <v>8.006415218810119</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.7050843466383679</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.4182700336033582</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>代理模型预测</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0.08316671217169065</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.1937147069549757</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.1937147069549757</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.1937147069549757</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.01250846256355071</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.3617328245449196</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.3617328245449196</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.3617328245449196</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.04361687878441518</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.5970539665622911</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.5970539665622911</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.5970539665622911</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.1188244796625885</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.4182700336033582</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.7050843466383679</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.7050843466383679</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1.842046672332326</v>
+      </c>
+      <c r="C8" t="n">
+        <v>7.6473638677</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>305.5270800864795</v>
+      </c>
+      <c r="F8" t="n">
+        <v>5.505645134039992</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5.704131325085113</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6932008430614239</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.4425833580692728</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>代理模型预测</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>0.09941444119002051</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.3447948276038513</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.3447948276038513</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.3447948276038513</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.03962782438078984</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.5591540080203735</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.5591540080203735</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.5591540080203735</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.1042177348950826</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.3950992390425537</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.3950992390425537</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.3950992390425537</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.05203446956400166</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.4425833580692728</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.6932008430614239</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.6932008430614239</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>2.210969369835105</v>
+      </c>
+      <c r="C9" t="n">
+        <v>7.790795789161787</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>303.9169721565574</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5.292942665486217</v>
+      </c>
+      <c r="G9" t="n">
+        <v>7.505602454720353</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.6917158625682558</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.4456803061984486</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>代理模型预测</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0.04203650026320394</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2405807221072792</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.2405807221072792</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.2405807221072792</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.01929302794988663</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.4817350353699934</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.4817350353699934</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.4817350353699934</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.07735621476764293</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.5531230223438907</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.5531230223438907</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.5531230223438907</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.1019816926156134</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.4456803061984486</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.6917158625682558</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.6917158625682558</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>2.518993712026152</v>
+      </c>
+      <c r="C10" t="n">
+        <v>7.366735135310019</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" t="n">
+        <v>302.3590664931828</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4.697435323147282</v>
+      </c>
+      <c r="G10" t="n">
+        <v>9.382731942264769</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.6901036821672694</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.449057621109196</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>代理模型预测</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0.06881019701670048</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.1397454040894993</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.1397454040894993</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.1397454040894993</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.006509592654712485</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.2649835939640238</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.2649835939640238</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.2649835939640238</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.02340543502336355</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.7177835037074359</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.7177835037074359</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.7177835037074359</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.1717377193981742</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.449057621109196</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.6901036821672694</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.6901036821672694</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>2.5150780354</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.176454549394275</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>305.2103287806643</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4.525987186613509</v>
+      </c>
+      <c r="G11" t="n">
+        <v>8.949563756408763</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.6895118217910809</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.4503014573446946</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>代理模型预测</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>0.002817951017620873</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.3242931249620933</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.3242931249620933</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.3242931249620933</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.03505534363255996</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.2025802815647083</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.2025802815647083</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.2025802815647083</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.01367959015961217</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.6797862944218213</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.6797862944218213</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.6797862944218213</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.1540364686945837</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.4503014573446946</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.6895118217910809</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.6895118217910809</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2.518993712026152</v>
+      </c>
+      <c r="C12" t="n">
+        <v>7.571311220157768</v>
+      </c>
+      <c r="D12" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" t="n">
+        <v>302.2670072549944</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4.758301179236547</v>
+      </c>
+      <c r="G12" t="n">
+        <v>9.392960746514946</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.6880184837602692</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.4534493238243243</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>代理模型预测</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0.08660356869191708</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.1337868773459156</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.1337868773459156</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.1337868773459156</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.005966309516657019</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.2871374132401055</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.2871374132401055</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.2871374132401055</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.0274826313607397</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.7186807672381532</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.7186807672381532</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.7186807672381532</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.1721673483993402</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.4534493238243243</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.6880184837602692</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.6880184837602692</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1.27239419591399</v>
+      </c>
+      <c r="C13" t="n">
+        <v>7.639004570316274</v>
+      </c>
+      <c r="D13" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" t="n">
+        <v>307.5242743616964</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5.651798324768997</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.724734616335958</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.6825801625012736</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.4650293913253509</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>代理模型预测</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>0.1839679396702808</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.4740630654819668</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.4740630654819668</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.4740630654819668</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.07491193001805319</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.6123505221593432</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.6123505221593432</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.6123505221593432</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.1249910539962734</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.2214679488013998</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.2214679488013998</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.2214679488013998</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.01634935078209981</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.4650293913253509</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.6825801625012736</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.6825801625012736</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1.50913088675831</v>
+      </c>
+      <c r="C14" t="n">
+        <v>5.788310496210959</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>308.3051010496245</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5.547296766425476</v>
+      </c>
+      <c r="G14" t="n">
+        <v>4.122386764850864</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.6789560964289825</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.472849283274089</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>代理模型预测</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>0.04966152265142003</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.5246020096844318</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.5246020096844318</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.5246020096844318</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.09173575618831489</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.5743142767771052</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.5743142767771052</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.5743142767771052</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.1099456295033365</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.256349716214988</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.256349716214988</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.256349716214988</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.0219050590011683</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.472849283274089</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.6789560964289825</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.6789560964289825</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="n">
+        <v>2.673878630389869</v>
+      </c>
+      <c r="C15" t="n">
+        <v>6.870601138731148</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" t="n">
+        <v>301.9687617216152</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4.455311017427628</v>
+      </c>
+      <c r="G15" t="n">
+        <v>10.32308237299908</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.6766913830235141</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.4777785340370609</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>代理模型预测</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0.1397742565569987</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.1144829593278479</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.1144829593278479</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.1144829593278479</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.00436878265882056</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.1768557262906729</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.1768557262906729</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.1768557262906729</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.01042598264060047</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.8002703835964105</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.8002703835964105</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.8002703835964105</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.213477562287182</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.4777785340370609</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.6766913830235141</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.6766913830235141</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>2.713713005951192</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2.998604542416721</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" t="n">
+        <v>303.5549105819708</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4.060484701208503</v>
+      </c>
+      <c r="G16" t="n">
+        <v>10.38701616143143</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.6746505850642501</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.4822487701611722</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>代理模型预测</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>0.08528023431570581</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2171463159851679</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.2171463159851679</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.2171463159851679</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.01571750751531013</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.0331477195860353</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.0331477195860353</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.0331477195860353</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.0003662571045848094</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.80587861065188</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.80587861065188</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.80587861065188</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.2164801117020682</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.4822487701611722</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.6746505850642501</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.6746505850642501</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1.001422122382009</v>
+      </c>
+      <c r="C17" t="n">
+        <v>7.530602713545091</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>308.8046874203997</v>
+      </c>
+      <c r="F17" t="n">
+        <v>5.808222789436702</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.979945656365591</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.6619365576016191</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.5107187970147459</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>代理模型预测</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0.0906696834184714</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.5569376971132514</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.5569376971132514</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.5569376971132514</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.1033931994886039</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.6692855518009845</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.6692855518009845</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.6692855518009845</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.1493143832831827</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.1561355838917185</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.1561355838917185</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.1561355838917185</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.008126106852402618</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.5107187970147459</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.6619365576016191</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.6619365576016191</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="n">
+        <v>2.834545825027642</v>
+      </c>
+      <c r="C18" t="n">
+        <v>6.870601138731148</v>
+      </c>
+      <c r="D18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E18" t="n">
+        <v>301.3424303692626</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4.342843981187304</v>
+      </c>
+      <c r="G18" t="n">
+        <v>11.38511009793478</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.6563828252617644</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.5235011665657181</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>代理模型预测</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0.1995287692822414</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.07394371322088204</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.07394371322088204</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.07394371322088204</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.001822557574964015</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.1359202239339728</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.1359202239339728</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.1359202239339728</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.006158102424753772</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.893430710345156</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.893430710345156</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.893430710345156</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.26607281139595</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.5235011665657181</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.6563828252617644</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.6563828252617644</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="n">
+        <v>2.905969922677872</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2.559821867854742</v>
+      </c>
+      <c r="D19" t="n">
+        <v>6</v>
+      </c>
+      <c r="E19" t="n">
+        <v>303.0071627844892</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3.959982013606025</v>
+      </c>
+      <c r="G19" t="n">
+        <v>11.66158452308101</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.6493045478334799</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.5401093421210091</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>代理模型预测</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>0.1520176055030006</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.181693384109334</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.181693384109334</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.181693384109334</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.01100416194303399</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-0.003433025694872432</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-0.003433025694872432</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.9176828529018431</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.9176828529018431</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.9176828529018431</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.2807139395033553</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.5401093421210091</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.6493045478334799</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.6493045478334799</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="n">
+        <v>2.906754824646826</v>
+      </c>
+      <c r="C20" t="n">
+        <v>6.870601138731148</v>
+      </c>
+      <c r="D20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E20" t="n">
+        <v>301.0643000864574</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4.292297681456906</v>
+      </c>
+      <c r="G20" t="n">
+        <v>11.8825983896383</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.6467420202657075</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.5462115784422977</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>代理模型预测</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0.1918928408383795</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.05594175316876595</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.05594175316876595</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.05594175316876595</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.001043159915865045</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.1175224938887466</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.1175224938887466</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.1175224938887466</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.004603845523276828</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.937070034178798</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.937070034178798</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.937070034178798</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.2927000829852845</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.5462115784422977</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.6467420202657075</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.6467420202657075</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="n">
+        <v>2.974228249771783</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3.78777656719211</v>
+      </c>
+      <c r="D21" t="n">
+        <v>6</v>
+      </c>
+      <c r="E21" t="n">
+        <v>302.193566032349</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3.855597307965588</v>
+      </c>
+      <c r="G21" t="n">
+        <v>12.20462924633007</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.6400885763350027</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.5622837791072071</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>代理模型预测</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0.08485475214414129</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.1290334001520395</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.1290334001520395</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.1290334001520395</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.005549872784932111</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-0.04142673928946503</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-0.04142673928946503</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.9653183549412344</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.9653183549412344</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.9653183549412344</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.3106131754621503</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.5622837791072071</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.6400885763350027</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.6400885763350027</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="n">
+        <v>0.7670387810769357</v>
+      </c>
+      <c r="C22" t="n">
+        <v>7.713118486475109</v>
+      </c>
+      <c r="D22" t="n">
+        <v>6</v>
+      </c>
+      <c r="E22" t="n">
+        <v>309.8115724740167</v>
+      </c>
+      <c r="F22" t="n">
+        <v>6.028825178760431</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.491674114379286</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.6384905349652212</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.5661939296476342</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>代理模型预测</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0.1148469985075524</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.6221082507454195</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.6221082507454195</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.6221082507454195</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.1290062252151752</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.7495799200882262</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.7495799200882262</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.7495799200882262</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.1872900188664905</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.113304746875376</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.113304746875376</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.113304746875376</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0.004279321888164338</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0.5661939296476342</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.6384905349652212</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.6384905349652212</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2.997357537989255</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2.998604542416721</v>
+      </c>
+      <c r="D23" t="n">
+        <v>5</v>
+      </c>
+      <c r="E23" t="n">
+        <v>302.9606707081776</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4.11193352877234</v>
+      </c>
+      <c r="G23" t="n">
+        <v>12.18091287967524</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.6384042039510439</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.5664057251049761</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>代理模型预测</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>0.1526278559735077</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.17868418823156</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.17868418823156</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.17868418823156</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.01064267970799052</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.05187394970993191</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.05187394970993191</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.05187394970993191</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.0008969688861695151</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.9632379719013372</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.9632379719013372</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.9632379719013372</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0.3092757968375337</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0.5664057251049761</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0.6384042039510439</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.6384042039510439</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" t="n">
+        <v>8</v>
+      </c>
+      <c r="D24" t="n">
+        <v>6</v>
+      </c>
+      <c r="E24" t="n">
+        <v>300.199999999962</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4.560000000012452</v>
+      </c>
+      <c r="G24" t="n">
+        <v>12.6000000000101</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.6287178032184325</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.5905387041387385</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>代理模型预测</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-2.461375224458291e-12</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-2.461375224458291e-12</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.2149601899324831</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.2149601899324831</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.2149601899324831</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.0154026277519364</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.000000000000886</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.000000000000886</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.000000000000886</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0.3333333333339241</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0.5905387041387385</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.6287178032184325</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.6287178032184325</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="n">
+        <v>0.684909164205926</v>
+      </c>
+      <c r="C25" t="n">
+        <v>8</v>
+      </c>
+      <c r="D25" t="n">
+        <v>6</v>
+      </c>
+      <c r="E25" t="n">
+        <v>310.0692742915963</v>
+      </c>
+      <c r="F25" t="n">
+        <v>6.180563585054175</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2.362920675901301</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.6265086496637609</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.5961471570052339</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>代理模型预测</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>0.1720099189774539</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.6387879800385995</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.6387879800385995</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.6387879800385995</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.1360166944805981</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.8048093285983475</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.8048093285983475</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.8048093285983475</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.2159060184663076</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.1020105856053773</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.1020105856053773</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.1020105856053773</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.003468719858517336</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0.5961471570052339</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0.6265086496637609</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.6265086496637609</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="n">
+        <v>0.5812813342019795</v>
+      </c>
+      <c r="C26" t="n">
+        <v>7.53914643547947</v>
+      </c>
+      <c r="D26" t="n">
+        <v>6</v>
+      </c>
+      <c r="E26" t="n">
+        <v>310.7685550309207</v>
+      </c>
+      <c r="F26" t="n">
+        <v>6.104908294448348</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.182422909191217</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.6250540558088286</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.5998616290970007</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>代理模型预测</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>0.1411259552027025</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.6840488693152538</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.6840488693152538</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.6840488693152538</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.1559742852038257</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.7772724837554383</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.7772724837554383</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.7772724837554383</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.2013841713344494</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.08617744817466814</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.08617744817466814</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.08617744817466814</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.002475517524632538</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0.5998616290970007</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0.6250540558088286</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.6250540558088286</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="n">
+        <v>0.6505371596</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3.558967609319518</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>313.7304184970495</v>
+      </c>
+      <c r="F27" t="n">
+        <v>6.233583723263797</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.63578669565522</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.5900968765649884</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.6946369989637935</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>代理模型预测</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>0.1010431663353364</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.8757552425274788</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.8757552425274788</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.8757552425274788</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.2556490816047877</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.8241074808853405</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.8241074808853405</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.8241074808853405</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.2263843800170606</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.03822690312765085</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.03822690312765085</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.03822690312765085</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0.000487098707576934</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0.6946369989637935</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.5900968765649884</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.5900968765649884</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="n">
+        <v>0.6389447448320311</v>
+      </c>
+      <c r="C28" t="n">
+        <v>2.621697004040366</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>314.2071627014172</v>
+      </c>
+      <c r="F28" t="n">
+        <v>6.291161384642153</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.570985314531526</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.5828161191628105</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.7158070395109452</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>代理模型预测</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>0.04209593978296683</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.9066124725836383</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.9066124725836383</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.9066124725836383</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.2739820584814061</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.8450644703449945</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.8450644703449945</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.8450644703449945</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.2380446530131554</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.03254257145013383</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.03254257145013383</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.03254257145013383</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0.000353006318862355</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0.7158070395109452</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0.5828161191628105</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.5828161191628105</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="n">
+        <v>0.5095605626375179</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2.869748941733312</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" t="n">
+        <v>314.7127405564617</v>
+      </c>
+      <c r="F29" t="n">
+        <v>6.361801283185001</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.405069807447781</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.5748521129900616</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.7395778451583925</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>代理模型预测</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>0.05639283582098592</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.939335958347034</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.939335958347034</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.939335958347034</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.2941173475479136</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.8707758239108403</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.8707758239108403</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.8707758239108403</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.2527501785025342</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.01798857960068253</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.01798857960068253</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.01798857960068253</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0.0001078629986833638</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0.7395778451583925</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.5748521129900616</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.5748521129900616</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="n">
+        <v>0.7670387810769357</v>
+      </c>
+      <c r="C30" t="n">
+        <v>7.505220729951497</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>311.9051264645582</v>
+      </c>
+      <c r="F30" t="n">
+        <v>6.964640162499778</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.881279226462548</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.5658468238687744</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.7672627252069016</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>代理模型预测</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>0.1165725944745343</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.7576133634018252</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.7576133634018252</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.7576133634018252</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.1913260028016753</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.090195781881179</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.090195781881179</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1.090195781881179</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0.3961756142771719</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0.05976133565460948</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0.05976133565460948</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.05976133565460948</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0.001190472413074299</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0.7672627252069016</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0.5658468238687744</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.5658468238687744</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="n">
+        <v>0.6815760182371708</v>
+      </c>
+      <c r="C31" t="n">
+        <v>7.573171561349142</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>312.2771018800379</v>
+      </c>
+      <c r="F31" t="n">
+        <v>7.04506241876596</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.736113620367659</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.5590444509831148</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.7887665251688613</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>代理模型预测</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>0.152508778562965</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.7816894420736511</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.7816894420736511</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.7816894420736511</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.2036794612831386</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.119467696310227</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.119467696310227</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1.119467696310227</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.4177359743607092</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0.04702751055856663</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.04702751055856663</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.04702751055856663</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0.0007371955831120318</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0.7887665251688613</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0.5590444509831148</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.5590444509831148</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="n">
+        <v>0.5543709101220426</v>
+      </c>
+      <c r="C32" t="n">
+        <v>7.997268161772953</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>312.6908401979296</v>
+      </c>
+      <c r="F32" t="n">
+        <v>7.271011836470334</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.568655935185924</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.5445392322820234</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.8364149738288975</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>代理模型预测</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>0.2267969193224826</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.8084686212252156</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.8084686212252156</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.8084686212252156</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.2178738371686003</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.201708264125743</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.201708264125743</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1.201708264125743</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0.481367584022702</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0.03233823992858982</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0.03233823992858982</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.03233823992858982</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0.0003485872538930136</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0.8364149738288975</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0.5445392322820234</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.5445392322820234</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="n">
+        <v>0.5039655324193715</v>
+      </c>
+      <c r="C33" t="n">
+        <v>7.998457641216467</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" t="n">
+        <v>312.9316626510793</v>
+      </c>
+      <c r="F33" t="n">
+        <v>7.306699820513415</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.504700391399963</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.5412429171409898</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.8475992356302879</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>代理模型预测</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>0.2446980164129398</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.8240558350213157</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.8240558350213157</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.8240558350213157</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.2263560064108926</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.214697897388415</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.214697897388415</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1.214697897388415</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0.4918303273066118</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0.02672810450876867</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0.02672810450876867</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.02672810450876867</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0.0002381305235438867</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0.8475992356302879</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0.5412429171409898</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.5412429171409898</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AK41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>推荐排序</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>case</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>flow_L_min</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>channel_mm</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>channels</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Tmax_K</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>deltaT_K</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>pump_W</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>_source_row</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>_data_role</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>约束1值</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>约束1违反量</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>搜索域内</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>最近样本距离</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>约束违反量</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>可行</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>综合效用</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>理想点距离</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>结果类型</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>归一化::Tmax_K</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>方向损失::Tmax_K</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>有效损失::Tmax_K</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>加权平方::Tmax_K</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>归一化::deltaT_K</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>方向损失::deltaT_K</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>有效损失::deltaT_K</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>加权平方::deltaT_K</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>归一化::pump_W</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>方向损失::pump_W</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>有效损失::pump_W</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>加权平方::pump_W</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>S_c</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>复算综合效用</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>效用复算差</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>"电池液冷"</t>
-        </is>
+          <t>SYNTHETIC_050</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2.1420804632</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.6322428126</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" t="n">
+        <v>305.5727901605</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4.438598346</v>
+      </c>
+      <c r="H2" t="n">
+        <v>7.0878225936</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>49</v>
+      </c>
+      <c r="K2" t="n">
+        <v>50</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>305.5727901605</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="b">
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.7284611613077201</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.3727567825370654</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>输入表实测/计算值</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>0.3477534084466033</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.3477534084466033</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.3477534084466033</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.04031081102874336</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.170772685219416</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.170772685219416</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.170772685219416</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.009721103339016584</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.5164756661052632</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.5164756661052632</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.5164756661052632</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.08891570455962511</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.3727567825370654</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.7284611613077201</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.7284611613077201</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>variables</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>["flow_L_min", "channel_mm", "channels"]</t>
-        </is>
+          <t>SYNTHETIC_059</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2.0073521177</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.0291515994</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>306.4560136965</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4.7854705422</v>
+      </c>
+      <c r="H3" t="n">
+        <v>6.2868126095</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>58</v>
+      </c>
+      <c r="K3" t="n">
+        <v>59</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>独立留出</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>306.4560136965</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.09465585797278739</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="b">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.72053743258258</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.3878529480637233</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>输入表实测/计算值</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0.4049199803559886</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.4049199803559886</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.4049199803559886</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.05465339683049808</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.2970264576997095</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.2970264576997095</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.2970264576997095</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.02940823885787911</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.4462116324122807</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.4462116324122807</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.4462116324122807</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.06636827363334409</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.3878529480637233</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.72053743258258</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.72053743258258</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>objectives</t>
-        </is>
+      <c r="A4" t="n">
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[{"column": "Tmax_K", "direction": "min", "unit": "K", "weight": 1}, {"column": "deltaT_K", "direction": "min", "unit": "K", "weight": 1}, {"column": "pump_W", "direction": "min", "unit": "W", "weight": 1}]</t>
-        </is>
+          <t>SYNTHETIC_040</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2.2210423504</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.7908635943</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>303.8255054549</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4.7526444107</v>
+      </c>
+      <c r="H4" t="n">
+        <v>7.6591781266</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>39</v>
+      </c>
+      <c r="K4" t="n">
+        <v>40</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>303.8255054549</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="b">
+        <v>1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="b">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.7191891753548412</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.3904547430189136</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>输入表实测/计算值</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>0.2346605472427191</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.2346605472427191</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.2346605472427191</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.0183551908107508</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.2850784751770068</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.2850784751770068</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.2850784751770068</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.02708991233641576</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.5665945725087719</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.5665945725087719</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.5665945725087719</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.1070098031987993</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.3904547430189136</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.7191891753548412</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.7191891753548412</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>constraints</t>
-        </is>
+      <c r="A5" t="n">
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[{"expression": "Tmax_K", "relation": "&lt;=", "limit": 315, "tolerance": 0, "scale": 10}]</t>
-        </is>
+          <t>SYNTHETIC_042</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1.8557962161</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.5929775628</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>307.2929749355</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4.8894288906</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5.5624243929</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>41</v>
+      </c>
+      <c r="K5" t="n">
+        <v>42</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>307.2929749355</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="b">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="b">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.7165728295395071</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.3955315618687808</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>输入表实测/计算值</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>0.4590922288349534</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.4590922288349534</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.4590922288349534</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.07025522485888172</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.3348649867317481</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.3348649867317481</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.3348649867317481</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.03737818644628461</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.3826688063947368</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.3826688063947368</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.3826688063947368</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.04881180512919085</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.3955315618687808</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.7165728295395071</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.7165728295395071</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
+      <c r="A6" t="n">
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>"RSM-Quadratic"</t>
-        </is>
+          <t>SYNTHETIC_025</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2.1913929116</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.0380498841</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>304.7863535727</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.8629318527</v>
+      </c>
+      <c r="H6" t="n">
+        <v>7.3145459659</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>24</v>
+      </c>
+      <c r="K6" t="n">
+        <v>25</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>304.7863535727</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="b">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="b">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.7139512803501245</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.4006557975631</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>输入表实测/计算值</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>0.296851363928805</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.296851363928805</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.296851363928805</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.02937357742213061</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.3252206536572708</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.3252206536572708</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.3252206536572708</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.03525615785508748</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.5363636812192982</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.5363636812192982</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.5363636812192982</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.09589533284370566</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.4006557975631</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.7139512803501245</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.7139512803501245</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>domain</t>
-        </is>
+      <c r="A7" t="n">
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>"box"</t>
-        </is>
+          <t>SYNTHETIC_014</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2.3573150682</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7.2257101425</v>
+      </c>
+      <c r="E7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" t="n">
+        <v>303.0732419611</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.7706018921</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8.429606703899999</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>13</v>
+      </c>
+      <c r="K7" t="n">
+        <v>14</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>303.0732419611</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="b">
+        <v>1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="b">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.70568917770054</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.4170544647694047</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>输入表实测/计算值</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>0.1859703534692562</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.1859703534692562</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.1859703534692562</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.01152832412316004</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.2916145994205523</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.2916145994205523</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.2916145994205523</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.02834635819840306</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.6341760266578946</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.6341760266578946</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.6341760266578946</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.1340597442625316</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.4170544647694047</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.70568917770054</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.70568917770054</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>max_distance</t>
-        </is>
+      <c r="A8" t="n">
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>null</t>
-        </is>
+          <t>SYNTHETIC_033</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1.4967395339</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3.8056984156</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>308.7517838901</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5.1399064188</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4.1285599995</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>32</v>
+      </c>
+      <c r="K8" t="n">
+        <v>33</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>308.7517838901</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="b">
+        <v>1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="b">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.699457233301864</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.4296799752565159</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>输入表实测/计算值</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>0.5535135203948232</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.5535135203948232</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.5535135203948232</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.1021257390866234</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.4260332417929163</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.4260332417929163</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.4260332417929163</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.06050144103752715</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.2568912280263158</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.2568912280263158</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.2568912280263158</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.02199770101228953</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.4296799752565159</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.699457233301864</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.699457233301864</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>validation</t>
-        </is>
+      <c r="A9" t="n">
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>"group"</t>
-        </is>
+          <t>SYNTHETIC_035</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2.5612304731</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5.091555402</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" t="n">
+        <v>303.2146280108</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4.2166295047</v>
+      </c>
+      <c r="H9" t="n">
+        <v>9.5264596139</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>34</v>
+      </c>
+      <c r="K9" t="n">
+        <v>35</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>303.2146280108</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="b">
+        <v>1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="b">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.6946564610493288</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.4395604965502339</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>输入表实测/计算值</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>0.19512155409709</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.19512155409709</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.19512155409709</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.01269080695775454</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.08998095877315382</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.08998095877315382</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.08998095877315382</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.002698857647245335</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.7303911942017545</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.7303911942017545</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.7303911942017545</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.1778237655224884</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.4395604965502339</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.6946564610493288</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.6946564610493288</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>folds</t>
-        </is>
+      <c r="A10" t="n">
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
+          <t>SYNTHETIC_039</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2.2974131022</v>
+      </c>
+      <c r="D10" t="n">
+        <v>7.6473638677</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>303.6272421408</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5.1868886331</v>
+      </c>
+      <c r="H10" t="n">
+        <v>7.9660965482</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>38</v>
+      </c>
+      <c r="K10" t="n">
+        <v>39</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>303.6272421408</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="b">
+        <v>1</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="b">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.6913682940336915</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.4464070866855059</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>输入表实测/计算值</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>0.2218279702783167</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.2218279702783167</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.2218279702783167</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.01640254946593258</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.4431337239296641</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.4431337239296641</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.4431337239296641</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.06545583242792391</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.5935172410701754</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.5935172410701754</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.5935172410701754</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.1174209051491843</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.4464070866855059</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.6913682940336915</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.6913682940336915</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>group_column</t>
-        </is>
+      <c r="A11" t="n">
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>"batch"</t>
-        </is>
+          <t>SYNTHETIC_019</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2.5150780354</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.1933622555</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>305.202720313</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.5238702179</v>
+      </c>
+      <c r="H11" t="n">
+        <v>8.9504091416</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>18</v>
+      </c>
+      <c r="K11" t="n">
+        <v>19</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>305.202720313</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="b">
+        <v>1</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="b">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.6896051037568757</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.4501052769942315</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>输入表实测/计算值</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>0.3238006675080907</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.3238006675080907</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.3238006675080907</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.03494895742622836</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.2018097519885955</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.2018097519885955</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.2018097519885955</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.01357572533256614</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.6798604510175438</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.6798604510175438</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.6798604510175438</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.1540700776192593</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.4501052769942315</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.6896051037568757</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.6896051037568757</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>time_column</t>
-        </is>
+      <c r="A12" t="n">
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>""</t>
-        </is>
+          <t>SYNTHETIC_060</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1.602291142</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4.2454397079</v>
+      </c>
+      <c r="E12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" t="n">
+        <v>308.5915638022</v>
+      </c>
+      <c r="G12" t="n">
+        <v>5.3257146208</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4.3930762699</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>59</v>
+      </c>
+      <c r="K12" t="n">
+        <v>60</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>独立留出</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>308.5915638022</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="b">
+        <v>1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.1365406493144893</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="b">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.6879641940636023</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.4535640206698749</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>输入表实测/计算值</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>0.5431432881682877</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.5431432881682877</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.5431432881682877</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.0983348771607532</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.4936632989646202</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.4936632989646202</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.4936632989646202</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.08123448424821067</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.2800944096403508</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0.2800944096403508</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.2800944096403508</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.02615095943725888</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.4535640206698749</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.6879641940636023</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.6879641940636023</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>holdout_column</t>
-        </is>
+      <c r="A13" t="n">
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>"batch"</t>
-        </is>
+          <t>SYNTHETIC_013</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1.6322714766</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5.8263005202</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="n">
+        <v>307.7496694177</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5.4673509204</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.5884872339</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>12</v>
+      </c>
+      <c r="K13" t="n">
+        <v>13</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>307.7496694177</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="b">
+        <v>1</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="b">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.6867129117727374</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.4562126077089733</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>输入表实测/计算值</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>0.4886517422459543</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.4886517422459543</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.4886517422459543</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.07959350840000216</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.5452157650906128</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.5452157650906128</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.5452157650906128</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.09908674350111407</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.2972357222719297</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.2972357222719297</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.2972357222719297</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.02944969153150525</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.4562126077089733</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.6867129117727374</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.6867129117727374</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>holdout_value</t>
-        </is>
+      <c r="A14" t="n">
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>"F"</t>
-        </is>
+          <t>SYNTHETIC_028</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1.4907992274</v>
+      </c>
+      <c r="D14" t="n">
+        <v>7.0998368145</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>307.2955737639</v>
+      </c>
+      <c r="G14" t="n">
+        <v>5.5927968082</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4.2719706443</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>27</v>
+      </c>
+      <c r="K14" t="n">
+        <v>28</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>307.2955737639</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="b">
+        <v>1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="b">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.6852943179903754</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.4592270412112835</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>输入表实测/计算值</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>0.459260437792881</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.459260437792881</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.459260437792881</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.0703067165739029</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.5908752810460447</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.5908752810460447</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.5908752810460447</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.1163778659170808</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.2694711091491228</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.2694711091491228</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.2694711091491228</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.02420489288868614</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.4592270412112835</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.6852943179903754</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.6852943179903754</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>duplicates</t>
-        </is>
+      <c r="A15" t="n">
+        <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>"reject"</t>
-        </is>
+          <t>SYNTHETIC_058</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2.5297468666</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.874805587</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>305.3375269944</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4.6973158038</v>
+      </c>
+      <c r="H15" t="n">
+        <v>8.9232833305</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>57</v>
+      </c>
+      <c r="K15" t="n">
+        <v>58</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>独立留出</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>305.3375269944</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="b">
+        <v>1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.221571922395127</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="b">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.6840932480244512</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.4617890220197839</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>输入表实测/计算值</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>0.3325260190550158</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.3325260190550158</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.3325260190550158</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.03685785111619225</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.2649400915771387</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.2649400915771387</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.2649400915771387</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.02339775070830088</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.6774809939035088</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0.6774809939035088</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.6774809939035088</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.1529934990334954</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.4617890220197839</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0.6840932480244512</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0.6840932480244512</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SYNTHETIC_038</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1.595372083</v>
+      </c>
+      <c r="D16" t="n">
+        <v>7.5744954465</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>306.6236590505</v>
+      </c>
+      <c r="G16" t="n">
+        <v>5.6558101587</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4.6829792724</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>37</v>
+      </c>
+      <c r="K16" t="n">
+        <v>38</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>306.6236590505</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="b">
+        <v>1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="b">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.6835493336875721</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.4629521977664117</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>输入表实测/计算值</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>0.4157708123300987</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.4157708123300987</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.4157708123300987</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.05762178946187672</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.6138107405737977</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.6138107405737977</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.6138107405737977</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.1255878750812513</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.3055244975789473</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0.3055244975789473</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.3055244975789473</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0.03111507287362273</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0.4629521977664117</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0.6835493336875721</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.6835493336875721</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SYNTHETIC_054</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1.3303169708</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6.7663160703</v>
+      </c>
+      <c r="E17" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>308.1575215628</v>
+      </c>
+      <c r="G17" t="n">
+        <v>5.6202046259</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3.712007695</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>53</v>
+      </c>
+      <c r="K17" t="n">
+        <v>54</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>独立留出</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>308.1575215628</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="b">
+        <v>1</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.08491536992602763</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="b">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.6782925533690755</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.4742901054021681</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>输入表实测/计算值</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>0.5150499393398078</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.5150499393398078</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.5150499393398078</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.08842548000464656</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.6008511177316749</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.6008511177316749</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.6008511177316749</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.120340688559801</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.2203515521929825</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0.2203515521929825</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.2203515521929825</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0.01618493551795222</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0.4742901054021681</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0.6782925533690755</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0.6782925533690755</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SYNTHETIC_048</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1.7601898595</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.9668035652</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>308.5336427666</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5.4572472498</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4.8662621879</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>47</v>
+      </c>
+      <c r="K18" t="n">
+        <v>48</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>308.5336427666</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="b">
+        <v>1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="b">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.6762415648402446</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.4787615136260374</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>输入表实测/计算值</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>0.5393943538252436</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.5393943538252436</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.5393943538252436</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.09698208964618402</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.5415382534793541</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.5415382534793541</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.5415382534793541</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.09775455999382307</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.3216019463070175</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0.3216019463070175</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.3216019463070175</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.03447593728948727</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0.4787615136260374</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0.6762415648402446</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0.6762415648402446</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SYNTHETIC_044</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1.4064909208</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3.5743694764</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" t="n">
+        <v>309.7547224737</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5.4541901987</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.6525785262</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>43</v>
+      </c>
+      <c r="K19" t="n">
+        <v>44</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>309.7547224737</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="b">
+        <v>1</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="b">
+        <v>1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.6710646147942241</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.4901694679679111</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>输入表实测/计算值</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>0.6184286390744339</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.6184286390744339</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.6184286390744339</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.1274846605424855</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.5404255548016617</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.5404255548016617</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.5404255548016617</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.09735326009422793</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.2151384672105263</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0.2151384672105263</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.2151384672105263</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0.01542818669123157</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0.4901694679679111</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0.6710646147942241</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0.6710646147942241</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SYNTHETIC_031</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1.3620034735</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3.3613208304</v>
+      </c>
+      <c r="E20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" t="n">
+        <v>310.0483989513</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5.4901404284</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.4941301956</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>30</v>
+      </c>
+      <c r="K20" t="n">
+        <v>31</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>310.0483989513</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="b">
+        <v>1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="b">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.6661938663136507</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.5010645557778074</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>输入表实测/计算值</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>0.6374368253268612</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.6374368253268612</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.6374368253268612</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.1354419020942624</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.5535106396567795</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.5535106396567795</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.5535106396567795</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0.1021246760710857</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.2012394908421053</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0.2012394908421053</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0.2012394908421053</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0.01349911089146326</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0.5010645557778074</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0.6661938663136507</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0.6661938663136507</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SYNTHETIC_053</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.9301416188</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.8806339807</v>
+      </c>
+      <c r="E21" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" t="n">
+        <v>311.226039301</v>
+      </c>
+      <c r="G21" t="n">
+        <v>5.3166327579</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.5822278162</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>52</v>
+      </c>
+      <c r="K21" t="n">
+        <v>53</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>独立留出</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>311.226039301</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="b">
+        <v>1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.1437584741526479</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="b">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.664541227171234</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.5047975341676244</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>输入表实测/计算值</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>0.7136595016828501</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.7136595016828501</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.7136595016828501</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.1697699614474046</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.490357702653255</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.490357702653255</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.490357702653255</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0.08015022551712601</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.1212480540526316</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0.1212480540526316</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0.1212480540526316</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0.00490036353718329</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0.5047975341676244</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0.664541227171234</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0.664541227171234</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SYNTHETIC_018</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1.3115016003</v>
+      </c>
+      <c r="D22" t="n">
+        <v>7.6239057189</v>
+      </c>
+      <c r="E22" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" t="n">
+        <v>307.8557417145</v>
+      </c>
+      <c r="G22" t="n">
+        <v>5.8697347005</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.6952390231</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>17</v>
+      </c>
+      <c r="K22" t="n">
+        <v>18</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>307.8557417145</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="b">
+        <v>1</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="b">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.6634668806061307</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.5072342406698871</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>输入表实测/计算值</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>0.4955172630744365</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.4955172630744365</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0.4955172630744365</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0.08184578600159342</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.6916745207333223</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.6916745207333223</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.6916745207333223</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0.159471214210557</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.2188806160614035</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0.2188806160614035</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0.2188806160614035</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0.01596957469580651</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0.5072342406698871</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0.6634668806061307</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0.6634668806061307</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SYNTHETIC_034</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2.8168158859</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3.4464749332</v>
+      </c>
+      <c r="E23" t="n">
+        <v>6</v>
+      </c>
+      <c r="F23" t="n">
+        <v>302.9518971978</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3.9694139786</v>
+      </c>
+      <c r="H23" t="n">
+        <v>11.0936658284</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>33</v>
+      </c>
+      <c r="K23" t="n">
+        <v>34</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>302.9518971978</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="b">
+        <v>1</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="b">
+        <v>1</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.6615917231057664</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.511506213085035</v>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>输入表实测/计算值</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>0.178116323482202</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.178116323482202</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0.178116323482202</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0.01057514156360548</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8678654235438598</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0.8678654235438598</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0.8678654235438598</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0.2510634644609877</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0.511506213085035</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0.6615917231057664</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0.6615917231057664</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SYNTHETIC_023</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8767240133</v>
+      </c>
+      <c r="D24" t="n">
+        <v>7.0763011709</v>
+      </c>
+      <c r="E24" t="n">
+        <v>6</v>
+      </c>
+      <c r="F24" t="n">
+        <v>309.5857734057</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5.7663643699</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.6761890531</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>22</v>
+      </c>
+      <c r="K24" t="n">
+        <v>23</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>309.5857734057</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="b">
+        <v>1</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="b">
+        <v>1</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.6575625659417786</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.520767835327994</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>输入表实测/计算值</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>0.6074934243171548</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.6074934243171548</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0.6074934243171548</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0.1230160868628609</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.6540500171156838</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.6540500171156838</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0.6540500171156838</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0.1425938082963421</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.1294902678157895</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0.1294902678157895</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0.1294902678157895</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0.005589243153001626</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0.520767835327994</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0.6575625659417786</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0.6575625659417786</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SYNTHETIC_045</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9191347128</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2.0184877491</v>
+      </c>
+      <c r="E25" t="n">
+        <v>6</v>
+      </c>
+      <c r="F25" t="n">
+        <v>311.6649686728</v>
+      </c>
+      <c r="G25" t="n">
+        <v>5.414031088</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.5146947319</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>44</v>
+      </c>
+      <c r="K25" t="n">
+        <v>45</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>311.6649686728</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="b">
+        <v>1</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="b">
+        <v>1</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.6538985912886326</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.5292891181021022</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>输入表实测/计算值</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>0.7420691697605191</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.7420691697605191</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.7420691697605191</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0.183555550903022</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0.5258085307770397</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.5258085307770397</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.5258085307770397</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0.09215820367930302</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.1153240992894737</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0.1153240992894737</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0.1153240992894737</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0.004433215958976128</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0.5292891181021022</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0.6538985912886326</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0.6538985912886326</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SYNTHETIC_027</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7037187836</v>
+      </c>
+      <c r="D26" t="n">
+        <v>4.9928047722</v>
+      </c>
+      <c r="E26" t="n">
+        <v>6</v>
+      </c>
+      <c r="F26" t="n">
+        <v>311.3336879599</v>
+      </c>
+      <c r="G26" t="n">
+        <v>5.5066793996</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.2439043902</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>26</v>
+      </c>
+      <c r="K26" t="n">
+        <v>27</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>311.3336879599</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="b">
+        <v>1</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="b">
+        <v>1</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.6538552523696098</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.5293904826426663</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>输入表实测/计算值</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>0.7206270524207117</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.7206270524207117</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.7206270524207117</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0.1731011162268544</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0.5595304577045166</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.5595304577045166</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.5595304577045166</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0.1043581110330086</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.09157056054385965</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0.09157056054385965</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0.09157056054385965</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0.002795055852772221</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0.5293904826426663</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0.6538552523696098</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0.6538552523696098</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SYNTHETIC_011</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.6980147436</v>
+      </c>
+      <c r="D27" t="n">
+        <v>5.6056408046</v>
+      </c>
+      <c r="E27" t="n">
+        <v>6</v>
+      </c>
+      <c r="F27" t="n">
+        <v>311.0848328363</v>
+      </c>
+      <c r="G27" t="n">
+        <v>5.5866257913</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2.264951539</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>10</v>
+      </c>
+      <c r="K27" t="n">
+        <v>11</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>311.0848328363</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="b">
+        <v>1</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="b">
+        <v>1</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.6524099155632015</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.5327786659047584</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>输入表实测/计算值</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>0.7045199246796126</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.7045199246796126</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0.7045199246796126</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0.1654494414235223</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.5886291680044119</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.5886291680044119</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.5886291680044119</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0.1154947658085221</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.09341680166666667</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0.09341680166666667</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0.09341680166666667</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0.002908899611209779</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0.5327786659047584</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0.6524099155632015</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0.6524099155632015</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SYNTHETIC_026</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>2.7285479023</v>
+      </c>
+      <c r="D28" t="n">
+        <v>7.6862458518</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" t="n">
+        <v>302.3874445863</v>
+      </c>
+      <c r="G28" t="n">
+        <v>5.1472777246</v>
+      </c>
+      <c r="H28" t="n">
+        <v>10.4182806787</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>25</v>
+      </c>
+      <c r="K28" t="n">
+        <v>26</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>302.3874445863</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="b">
+        <v>1</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="b">
+        <v>1</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.6515932837054816</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.5346996738720179</v>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>输入表实测/计算值</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>0.1415821738705496</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.1415821738705496</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0.1415821738705496</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0.006681837319303508</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0.4287162333256805</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.4287162333256805</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0.4287162333256805</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0.06126586957231978</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8086211121666668</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0.8086211121666668</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0.8086211121666668</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0.217956034347219</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0.5346996738720179</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0.6515932837054816</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0.6515932837054816</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SYNTHETIC_049</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1.2061323954</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2.74587235</v>
+      </c>
+      <c r="E29" t="n">
+        <v>4</v>
+      </c>
+      <c r="F29" t="n">
+        <v>311.0246465367</v>
+      </c>
+      <c r="G29" t="n">
+        <v>5.6335382167</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2.9830000437</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>48</v>
+      </c>
+      <c r="K29" t="n">
+        <v>49</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>311.0246465367</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="b">
+        <v>1</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.6483892200209761</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.54228350676103</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>输入表实测/计算值</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>0.7006243713074449</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.7006243713074449</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0.7006243713074449</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0.1636248365566508</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.6057042485321555</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.6057042485321555</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.6057042485321555</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0.1222925455633011</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.1564035126052632</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0.1564035126052632</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0.1564035126052632</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0.008154019585088237</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0.54228350676103</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0.6483892200209761</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0.6483892200209761</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SYNTHETIC_052</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2.9654841966</v>
+      </c>
+      <c r="D30" t="n">
+        <v>5.0950830762</v>
+      </c>
+      <c r="E30" t="n">
+        <v>6</v>
+      </c>
+      <c r="F30" t="n">
+        <v>301.6386109369</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3.9340310017</v>
+      </c>
+      <c r="H30" t="n">
+        <v>12.2076699779</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>51</v>
+      </c>
+      <c r="K30" t="n">
+        <v>52</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>独立留出</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>301.6386109369</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="b">
+        <v>1</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.1617025582800854</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="b">
+        <v>1</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.6409981553586104</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0.5600668919874563</v>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>输入表实测/计算值</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>0.09311397649838413</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.09311397649838413</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0.09311397649838413</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0.002890070873113877</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-0.01287861743935319</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-0.01287861743935319</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9655850857807018</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0.9655850857807018</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0.9655850857807018</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0.3107848526273751</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0.5600668919874563</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0.6409981553586104</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0.6409981553586104</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SYNTHETIC_022</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.5387383193</v>
+      </c>
+      <c r="D31" t="n">
+        <v>5.6348867737</v>
+      </c>
+      <c r="E31" t="n">
+        <v>6</v>
+      </c>
+      <c r="F31" t="n">
+        <v>311.8286571507</v>
+      </c>
+      <c r="G31" t="n">
+        <v>5.7024951025</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2.0300311107</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>21</v>
+      </c>
+      <c r="K31" t="n">
+        <v>22</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>311.8286571507</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="b">
+        <v>1</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="b">
+        <v>1</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.6375351310326698</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.5685410126030467</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>输入表实测/计算值</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>0.752663893249192</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.752663893249192</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0.752663893249192</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0.1888343120670103</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0.6308030228534133</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.6308030228534133</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.6308030228534133</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0.1326374845470012</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.07280974655263157</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0.07280974655263157</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0.07280974655263157</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0.001767086397686148</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0.5685410126030467</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0.6375351310326698</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0.6375351310326698</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SYNTHETIC_021</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>2.8554843223</v>
+      </c>
+      <c r="D32" t="n">
+        <v>7.9366952477</v>
+      </c>
+      <c r="E32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" t="n">
+        <v>302.28182367</v>
+      </c>
+      <c r="G32" t="n">
+        <v>5.3897976583</v>
+      </c>
+      <c r="H32" t="n">
+        <v>11.1313836202</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>20</v>
+      </c>
+      <c r="K32" t="n">
+        <v>21</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>302.28182367</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="b">
+        <v>1</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="b">
+        <v>1</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.6289221819805829</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0.5900218320346564</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>输入表实测/计算值</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>0.1347458686084147</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.1347458686084147</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0.1347458686084147</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0.006052149702345386</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0.5169881007936666</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.5169881007936666</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.5169881007936666</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0.08909223212074747</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8711740017719298</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0.8711740017719298</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0.8711740017719298</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0.2529813804544395</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0.5900218320346564</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0.6289221819805829</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0.6289221819805829</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>SYNTHETIC_002</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" t="n">
+        <v>8</v>
+      </c>
+      <c r="E33" t="n">
+        <v>6</v>
+      </c>
+      <c r="F33" t="n">
+        <v>300.2</v>
+      </c>
+      <c r="G33" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="H33" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>300.2</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="b">
+        <v>1</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="b">
+        <v>1</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.6287178032188476</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0.5905387041376883</v>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>输入表实测/计算值</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0.2149601899279507</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.2149601899279507</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.2149601899279507</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0.01540262775128688</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0.5905387041376883</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0.6287178032188476</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0.6287178032188476</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SYNTHETIC_024</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.685421722</v>
+      </c>
+      <c r="D34" t="n">
+        <v>3.3255279273</v>
+      </c>
+      <c r="E34" t="n">
+        <v>5</v>
+      </c>
+      <c r="F34" t="n">
+        <v>312.6703644101</v>
+      </c>
+      <c r="G34" t="n">
+        <v>5.7149118562</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.9800399208</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>23</v>
+      </c>
+      <c r="K34" t="n">
+        <v>24</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>312.6703644101</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="b">
+        <v>1</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="b">
+        <v>1</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.6272103171146574</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0.594361528681925</v>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>输入表实测/计算值</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>0.807143327514563</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0.807143327514563</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0.807143327514563</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0.217160117050427</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0.6353224453201239</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.6353224453201239</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.6353224453201239</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0.134544869842514</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.06842455445614035</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0.06842455445614035</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0.06842455445614035</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0.001560639884173772</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0.594361528681925</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0.6272103171146574</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0.6272103171146574</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SYNTHETIC_012</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.7591144347</v>
+      </c>
+      <c r="D35" t="n">
+        <v>7.079947697</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4</v>
+      </c>
+      <c r="F35" t="n">
+        <v>311.1337023078</v>
+      </c>
+      <c r="G35" t="n">
+        <v>6.3496619623</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2.1455030548</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>11</v>
+      </c>
+      <c r="K35" t="n">
+        <v>12</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>311.1337023078</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="b">
+        <v>1</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="b">
+        <v>1</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.6069328233815268</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0.6476288008753572</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>输入表实测/计算值</t>
+        </is>
+      </c>
+      <c r="V35" t="n">
+        <v>0.7076829972686083</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.7076829972686083</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0.7076829972686083</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0.1669384082076937</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0.8663573808246828</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.8663573808246828</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.8663573808246828</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0.2501917037698015</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.08293886445614033</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0.08293886445614033</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0.08293886445614033</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0.002292951745758006</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0.6476288008753572</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0.6069328233815268</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0.6069328233815268</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SYNTHETIC_037</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6207599354</v>
+      </c>
+      <c r="D36" t="n">
+        <v>7.8387205786</v>
+      </c>
+      <c r="E36" t="n">
+        <v>5</v>
+      </c>
+      <c r="F36" t="n">
+        <v>310.9458446423</v>
+      </c>
+      <c r="G36" t="n">
+        <v>6.421673484</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2.1043475057</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>36</v>
+      </c>
+      <c r="K36" t="n">
+        <v>37</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>310.9458446423</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="b">
+        <v>1</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="b">
+        <v>1</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.6042622032909728</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0.654910723447096</v>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>输入表实测/计算值</t>
+        </is>
+      </c>
+      <c r="V36" t="n">
+        <v>0.6955239250679635</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0.6955239250679635</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0.6955239250679635</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0.1612511767806487</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0.8925679747444949</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.8925679747444949</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.8925679747444949</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0.2655591965131631</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.07932872857017542</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0.07932872857017542</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0.07932872857017542</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0.002097682392186855</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0.654910723447096</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0.6042622032909728</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0.6042622032909728</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SYNTHETIC_046</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6950253206</v>
+      </c>
+      <c r="D37" t="n">
+        <v>7.0503960042</v>
+      </c>
+      <c r="E37" t="n">
+        <v>4</v>
+      </c>
+      <c r="F37" t="n">
+        <v>311.4488072346</v>
+      </c>
+      <c r="G37" t="n">
+        <v>6.386686827</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2.0321920357</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>45</v>
+      </c>
+      <c r="K37" t="n">
+        <v>46</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>311.4488072346</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="b">
+        <v>1</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="b">
+        <v>1</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.6021593411739131</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0.6606900061543415</v>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>输入表实测/计算值</t>
+        </is>
+      </c>
+      <c r="V37" t="n">
+        <v>0.7280781381618133</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0.7280781381618133</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0.7280781381618133</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0.1766992584230575</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0.8798336089431574</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.8798336089431574</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.8798336089431574</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0.2580357264753136</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.07299930137719299</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0.07299930137719299</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0.07299930137719299</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0.00177629933385275</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0.6606900061543415</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0.6021593411739131</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0.6021593411739131</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SYNTHETIC_057</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.79862305</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2.9858767267</v>
+      </c>
+      <c r="E38" t="n">
+        <v>3</v>
+      </c>
+      <c r="F38" t="n">
+        <v>313.290799978</v>
+      </c>
+      <c r="G38" t="n">
+        <v>6.15181924</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1.8646523676</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>56</v>
+      </c>
+      <c r="K38" t="n">
+        <v>57</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>独立留出</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>313.290799978</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="b">
+        <v>1</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.06216341050179246</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="b">
+        <v>1</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.5983033607628545</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0.6713929180089683</v>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>输入表实测/计算值</t>
+        </is>
+      </c>
+      <c r="V38" t="n">
+        <v>0.8473009694498392</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0.8473009694498392</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0.8473009694498392</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0.2393063109435458</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0.7943470256512632</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.7943470256512632</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0.7943470256512632</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0.2103290657203362</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.05830283926315789</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0.05830283926315789</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0.05830283926315789</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0.001133073688715208</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0.6713929180089683</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0.5983033607628545</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0.5983033607628545</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>SYNTHETIC_008</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.9270614979</v>
+      </c>
+      <c r="D39" t="n">
+        <v>7.631076422</v>
+      </c>
+      <c r="E39" t="n">
+        <v>3</v>
+      </c>
+      <c r="F39" t="n">
+        <v>310.6025967249</v>
+      </c>
+      <c r="G39" t="n">
+        <v>6.6410671192</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2.3628854461</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>7</v>
+      </c>
+      <c r="K39" t="n">
+        <v>8</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>310.6025967249</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="b">
+        <v>1</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="b">
+        <v>1</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.5933280521589543</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0.6854082600026755</v>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>输入表实测/计算值</t>
+        </is>
+      </c>
+      <c r="V39" t="n">
+        <v>0.6733072313851161</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0.6733072313851161</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0.6733072313851161</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0.1511142092784967</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0.9724223833872516</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.9724223833872516</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0.9724223833872516</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0.315201763904181</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.1020074952719298</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0.1020074952719298</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0.1020074952719298</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0.003468509697217595</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0.6854082600026755</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0.5933280521589543</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0.5933280521589543</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SYNTHETIC_006</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.5800208733</v>
+      </c>
+      <c r="D40" t="n">
+        <v>4.8184795071</v>
+      </c>
+      <c r="E40" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" t="n">
+        <v>313.498864698</v>
+      </c>
+      <c r="G40" t="n">
+        <v>6.327151327</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1.5946330315</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>5</v>
+      </c>
+      <c r="K40" t="n">
+        <v>6</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>313.498864698</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="b">
+        <v>1</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="b">
+        <v>1</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0.5875315063893712</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0.7020363829429703</v>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>输入表实测/计算值</t>
+        </is>
+      </c>
+      <c r="V40" t="n">
+        <v>0.8607679416181229</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0.8607679416181229</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0.8607679416181229</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0.2469738164391667</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0.8581640097252179</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0.8581640097252179</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0.8581640097252179</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0.2454818225292213</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.03461693258771929</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0.03461693258771929</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0.03461693258771929</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0.0003994440072609006</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0.7020363829429703</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0.5875315063893712</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0.5875315063893712</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>SYNTHETIC_030</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.6505371596</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2.8727356484</v>
+      </c>
+      <c r="E41" t="n">
+        <v>3</v>
+      </c>
+      <c r="F41" t="n">
+        <v>314.0392228794</v>
+      </c>
+      <c r="G41" t="n">
+        <v>6.262907698</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1.6014750977</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>29</v>
+      </c>
+      <c r="K41" t="n">
+        <v>30</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>314.0392228794</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="b">
+        <v>1</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="b">
+        <v>1</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0.5857497289268123</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0.7072137648824197</v>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>输入表实测/计算值</t>
+        </is>
+      </c>
+      <c r="V41" t="n">
+        <v>0.8957425811909381</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0.8957425811909381</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0.8957425811909381</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0.2674515905862014</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0.8347807561582535</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0.8347807561582535</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0.8347807561582535</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0.2322863036173818</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.03521711383333334</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0.03521711383333334</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0.03521711383333334</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0.0004134150355833195</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0.7072137648824197</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0.5857497289268123</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0.5857497289268123</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>generations</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>runs</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>decision</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>"IDEAL"</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>sources</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>"合成函数演示数据，只用于软件功能测试，不代表真实试验或仿真结果。"</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>responses</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>mode</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>"general"</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>problem</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>{"name": "电池液冷", "variables": [{"column": "flow_L_min", "lower": 0.5, "upper": 3, "unit": "L/min", "kind": "continuous", "allowed": []}, {"column": "channel_mm", "lower": 2, "upper": 8, "unit": "mm", "kind": "continuous", "allowed": []}, {"column": "channels", "lower": 2, "upper": 6, "unit": "", "kind": "integer", "allowed": []}], "objectives": [{"column": "Tmax_K", "direction": "min", "unit": "K", "weight": 1}, {"column": "deltaT_K", "direction": "min", "unit": "K", "weight": 1}, {"column": "pump_W", "direction": "min", "unit": "W", "weight": 1}], "constraints": [{"expression": "Tmax_K", "relation": "&lt;=", "limit": 315, "tolerance": 0, "scale": 10}], "model": "RSM-Quadratic", "domain": "box", "max_distance": null, "validation": "group", "folds": 5, "group_column": "batch", "time_column": "", "holdout_column": "batch", "holdout_value": "F", "duplicates": "reject", "seed": 42, "population": 32, "generations": 10, "runs": 1, "decision": "IDEAL", "sources": [], "description": "合成函数演示数据，只用于软件功能测试，不代表真实试验或仿真结果。", "responses": []}</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>target_names</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>["Tmax_K", "deltaT_K", "pump_W"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>software_version</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>"0.2.0"</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>directions</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>["min", "min", "min"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>normalized_weights</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>[0.3333333333333333, 0.3333333333333333, 0.3333333333333333]</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>decision_method</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>"IDEAL"</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>anchor_minimum</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>[300.2, 3.9694139786, 1.2]</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>anchor_maximum</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>[315.65, 6.716834427, 12.6]</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>anchor_source</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>"training_only_before_search"</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>search_lower</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>[0.5, 2.0, 2.0]</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>search_upper</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>[3.0, 8.0, 6.0]</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>sample_count</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>holdout_count</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>cv</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>"按指定分组验证"</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>cv_folds</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>cv_fold_sizes</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>[{"train": 40, "validation": 10}, {"train": 40, "validation": 10}, {"train": 40, "validation": 10}, {"train": 40, "validation": 10}, {"train": 40, "validation": 10}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>cv_seed</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>model_selection</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>"最小CV NRMSE；选型与报告共用折，非嵌套验证"</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>selected_models</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>{"Tmax_K": "RSM-Quadratic", "deltaT_K": "RSM-Quadratic", "pump_W": "RSM-Quadratic"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>library_versions</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>{"python": "3.13.2", "numpy": "2.2.5", "pandas": "2.3.3", "scipy": "1.14.1", "sklearn": "1.7.0"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>clean_data_sha256</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>"02b01a0b9940b22e2b5fe3d3f6153985a9bc91a891c8c06f717c8912b50045d0"</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>source_sha256</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>browser_runtime</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>{"platform": "emscripten", "python": "3.13.2", "numpy": "2.2.5", "pandas": "2.3.3", "scipy": "1.14.1", "sklearn": "1.7.0", "openpyxl": "3.1.5", "pyodide": "0.29.3", "source_sha256": {"mtpv_optimizer/__init__.py": "c5393d3218aca0011f762aefd1443bed0233cfea21e009e6328c0d66d7319bd6", "mtpv_optimizer/core.py": "f0f770bb2813cb503f297b96c80c198b32d1b10d141fd8448085aacda1bc417b", "mtpv_optimizer/coupled.py": "a6869ea24416dc86fc2611f4511ae75dae03c2f2902c54dd3f8a36d388a48d80", "mtpv_optimizer/dat_parser.py": "059582ea4a4f64574b5ed5854ecba11a1bd4a699082a583dacc3c116b25a5fde", "mtpv_optimizer/doe.py": "cbd571d6f4d589f7c057e1cfacbae60c71809ee8be0dd7b11e29f4297e8fd90a", "mtpv_optimizer/domain.py": "5def038bde5d6422f462b721e910440dc5a00ae4f4059b0f31fd053c0071eb20", "mtpv_optimizer/general.py": "2329afad04dd1efdab8dde0e455fbda7e7fcefc90f7b3734abee6c11e4339eb7", "mtpv_optimizer/nsga2.py": "0541ee280ba369059c0b42397cb957975d2577d65576a1813f44f53b3bce688d", "mtpv_optimizer/presets.py": "19622217b24e6c5dbc6f3965f7d8e7b6740409e430af27e756222a8f7dcc2b30", "mtpv_optimizer/problem.py": "71200acc9ff03474b9f61206d365e1a9785008be3e6dc68fdd7fe9a06414a4bb", "mtpv_optimizer/workflow.py": "ca506ec953ec039e31653a23ee09d6289402a242e460705fa7326bc3bda0ef71"}, "scope": "General numerical-table workflow; no Qt, no private research records.", "browser_adjustment": "Forest estimators run with n_jobs=1 in the browser."}</t>
-        </is>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>generation</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>feasible_count</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nondominated_count</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>reference_ideal_utility</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.7284611613082896</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>42</v>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D3" t="n">
+        <v>32</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.7284611613082896</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>32</v>
+      </c>
+      <c r="D4" t="n">
+        <v>32</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.7284611613082896</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>32</v>
+      </c>
+      <c r="D5" t="n">
+        <v>32</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.7284611613082896</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>42</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>32</v>
+      </c>
+      <c r="D6" t="n">
+        <v>32</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.7331603280321375</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>42</v>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="n">
+        <v>32</v>
+      </c>
+      <c r="D7" t="n">
+        <v>32</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.7331603280321375</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>42</v>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="n">
+        <v>32</v>
+      </c>
+      <c r="D8" t="n">
+        <v>32</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.7331603280321375</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>42</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="n">
+        <v>32</v>
+      </c>
+      <c r="D9" t="n">
+        <v>32</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.7331603280321375</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="n">
+        <v>32</v>
+      </c>
+      <c r="D10" t="n">
+        <v>32</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.7262659798652369</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>42</v>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="n">
+        <v>32</v>
+      </c>
+      <c r="D11" t="n">
+        <v>32</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.7262659798652369</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>flow_L_min</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>channel_mm</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>channels</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Tmax_K</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>deltaT_K</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>pump_W</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>flow_L_min</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.04840466036664581</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.06902701727423816</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.9597578807346536</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.8321095689014797</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.985186566952941</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>channel_mm</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.04840466036664581</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.03626990787629383</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.2684280018552864</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2368331844054891</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.06943021837695076</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>channels</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.06902701727423816</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.03626990787629383</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.2428773599101485</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.499205789862264</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.114302877881105</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Tmax_K</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>-0.9597578807346536</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.2684280018552864</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.2428773599101485</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.8145658141493877</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.9539759835068935</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>deltaT_K</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>-0.8321095689014797</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.2368331844054891</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.499205789862264</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.8145658141493877</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.8292135853019759</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>pump_W</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.985186566952941</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.06943021837695076</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.114302877881105</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.9539759835068935</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.8292135853019759</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>flow_L_min</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>channel_mm</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>channels</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Tmax_K</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>deltaT_K</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>pump_W</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>flow_L_min</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.06698679471788715</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.03714120106201409</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.9408403361344538</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.8290516206482593</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9872268907563025</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>channel_mm</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.06698679471788715</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.04196857202232893</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.2943097238895558</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2241056422569028</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1103961584633854</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>channels</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.03714120106201409</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.04196857202232893</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.2113206267321492</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.4472214382520239</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.1297971681676487</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Tmax_K</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>-0.9408403361344538</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.2943097238895558</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.2113206267321492</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.797358943577431</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.9654261704681872</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>deltaT_K</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>-0.8290516206482593</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.2241056422569028</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.4472214382520239</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.797358943577431</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.8473949579831933</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>pump_W</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.9872268907563025</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.1103961584633854</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.1297971681676487</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.9654261704681872</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.8473949579831933</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>flow_L_min</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>channel_mm</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>channels</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Tmax_K</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>deltaT_K</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>pump_W</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>flow_L_min</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>50</v>
+      </c>
+      <c r="C2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>channel_mm</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>50</v>
+      </c>
+      <c r="C3" t="n">
+        <v>50</v>
+      </c>
+      <c r="D3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G3" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>channels</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>50</v>
+      </c>
+      <c r="C4" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E4" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" t="n">
+        <v>50</v>
+      </c>
+      <c r="G4" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Tmax_K</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>50</v>
+      </c>
+      <c r="C5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D5" t="n">
+        <v>50</v>
+      </c>
+      <c r="E5" t="n">
+        <v>50</v>
+      </c>
+      <c r="F5" t="n">
+        <v>50</v>
+      </c>
+      <c r="G5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>deltaT_K</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>50</v>
+      </c>
+      <c r="C6" t="n">
+        <v>50</v>
+      </c>
+      <c r="D6" t="n">
+        <v>50</v>
+      </c>
+      <c r="E6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G6" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>pump_W</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>50</v>
+      </c>
+      <c r="C7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" t="n">
+        <v>50</v>
+      </c>
+      <c r="E7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F7" t="n">
+        <v>50</v>
+      </c>
+      <c r="G7" t="n">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -11695,6 +19935,596 @@
       <c r="U41" t="inlineStr">
         <is>
           <t>输入表实测/计算值</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>设置</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>"电池液冷"</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>variables</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>["flow_L_min", "channel_mm", "channels"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>objectives</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>[{"column": "Tmax_K", "direction": "min", "unit": "K", "weight": 1}, {"column": "deltaT_K", "direction": "min", "unit": "K", "weight": 1}, {"column": "pump_W", "direction": "min", "unit": "W", "weight": 1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>constraints</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>[{"expression": "Tmax_K", "relation": "&lt;=", "limit": 315, "tolerance": 0, "scale": 10}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>"RSM-Quadratic"</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>domain</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>"box"</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>max_distance</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>"group"</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>folds</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>group_column</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>"batch"</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>time_column</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>holdout_column</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>"batch"</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>holdout_value</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>"F"</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>duplicates</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>"reject"</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>generations</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>runs</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>"IDEAL"</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>"合成函数演示数据，只用于软件功能测试，不代表真实试验或仿真结果。"</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>responses</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>mode</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>"general"</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>problem</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>{"name": "电池液冷", "variables": [{"column": "flow_L_min", "lower": 0.5, "upper": 3, "unit": "L/min", "kind": "continuous", "allowed": []}, {"column": "channel_mm", "lower": 2, "upper": 8, "unit": "mm", "kind": "continuous", "allowed": []}, {"column": "channels", "lower": 2, "upper": 6, "unit": "", "kind": "integer", "allowed": []}], "objectives": [{"column": "Tmax_K", "direction": "min", "unit": "K", "weight": 1}, {"column": "deltaT_K", "direction": "min", "unit": "K", "weight": 1}, {"column": "pump_W", "direction": "min", "unit": "W", "weight": 1}], "constraints": [{"expression": "Tmax_K", "relation": "&lt;=", "limit": 315, "tolerance": 0, "scale": 10}], "model": "RSM-Quadratic", "domain": "box", "max_distance": null, "validation": "group", "folds": 5, "group_column": "batch", "time_column": "", "holdout_column": "batch", "holdout_value": "F", "duplicates": "reject", "seed": 42, "population": 32, "generations": 10, "runs": 1, "decision": "IDEAL", "sources": [], "description": "合成函数演示数据，只用于软件功能测试，不代表真实试验或仿真结果。", "responses": []}</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>target_names</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>["Tmax_K", "deltaT_K", "pump_W"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>software_version</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>"0.2.0"</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>directions</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>["min", "min", "min"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>normalized_weights</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>[0.3333333333333333, 0.3333333333333333, 0.3333333333333333]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>decision_method</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>"IDEAL"</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>anchor_minimum</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>[300.2, 3.9694139786, 1.2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>anchor_maximum</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>[315.65, 6.716834427, 12.6]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>anchor_source</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>"training_only_before_search"</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>search_lower</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>[0.5, 2.0, 2.0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>search_upper</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>[3.0, 8.0, 6.0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>sample_count</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>holdout_count</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>cv</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>"按指定分组验证"</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>cv_folds</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>cv_fold_sizes</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>[{"train": 40, "validation": 10}, {"train": 40, "validation": 10}, {"train": 40, "validation": 10}, {"train": 40, "validation": 10}, {"train": 40, "validation": 10}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>cv_seed</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>model_selection</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>"最小CV NRMSE；选型与报告共用折，非嵌套验证"</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>selected_models</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>{"Tmax_K": "RSM-Quadratic", "deltaT_K": "RSM-Quadratic", "pump_W": "RSM-Quadratic"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>library_versions</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>{"python": "3.13.2", "numpy": "2.2.5", "pandas": "2.3.3", "scipy": "1.14.1", "sklearn": "1.7.0"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>clean_data_sha256</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>"02b01a0b9940b22e2b5fe3d3f6153985a9bc91a891c8c06f717c8912b50045d0"</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>source_sha256</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>calculation_audit</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>{"training": {"fit_attempts": 18, "fits_completed": 18, "candidate_families": ["RSM-Quadratic"], "response_count": 3, "validation_folds": 5, "validation_timings": [{"target": "Tmax_K", "model": "RSM-Quadratic", "seconds": 0.0829000000000022}, {"target": "deltaT_K", "model": "RSM-Quadratic", "seconds": 0.046299999999998676}, {"target": "pump_W", "model": "RSM-Quadratic", "seconds": 0.04649999999999821}]}, "search": {"objective_vector_rows": 992, "objective_prediction_batches": 21, "population_size": 32, "generations": 10, "runs": 1, "semantics": "Rows requested from the objective surrogate, including repeated evaluations; not CFD solves or unique designs."}, "selected_model_parameters": {"Tmax_K": {"memory": "None", "steps": "[('poly', PolynomialFeatures(include_bias=False)), ('scale', StandardScaler()), ('regression', LinearRegression(n_jobs=1))]", "transform_input": "None", "verbose": "False", "poly": "PolynomialFeatures(include_bias=False)", "scale": "StandardScaler()", "regression": "LinearRegression(n_jobs=1)", "poly__degree": "2", "poly__include_bias": "False", "poly__interaction_only": "False", "poly__order": "C", "scale__copy": "True", "scale__with_mean": "True", "scale__with_std": "True", "regression__copy_X": "True", "regression__fit_intercept": "True", "regression__n_jobs": "1", "regression__positive": "False", "regression__tol": "1e-06"}, "deltaT_K": {"memory": "None", "steps": "[('poly', PolynomialFeatures(include_bias=False)), ('scale', StandardScaler()), ('regression', LinearRegression(n_jobs=1))]", "transform_input": "None", "verbose": "False", "poly": "PolynomialFeatures(include_bias=False)", "scale": "StandardScaler()", "regression": "LinearRegression(n_jobs=1)", "poly__degree": "2", "poly__include_bias": "False", "poly__interaction_only": "False", "poly__order": "C", "scale__copy": "True", "scale__with_mean": "True", "scale__with_std": "True", "regression__copy_X": "True", "regression__fit_intercept": "True", "regression__n_jobs": "1", "regression__positive": "False", "regression__tol": "1e-06"}, "pump_W": {"memory": "None", "steps": "[('poly', PolynomialFeatures(include_bias=False)), ('scale', StandardScaler()), ('regression', LinearRegression(n_jobs=1))]", "transform_input": "None", "verbose": "False", "poly": "PolynomialFeatures(include_bias=False)", "scale": "StandardScaler()", "regression": "LinearRegression(n_jobs=1)", "poly__degree": "2", "poly__include_bias": "False", "poly__interaction_only": "False", "poly__order": "C", "scale__copy": "True", "scale__with_mean": "True", "scale__with_std": "True", "regression__copy_X": "True", "regression__fit_intercept": "True", "regression__n_jobs": "1", "regression__positive": "False", "regression__tol": "1e-06"}}, "runtime_seconds": {"preprocessing": 0.05099999999999838, "model_validation_and_fit": 0.2703000000000024, "holdout_and_constraints": 0.044299999999999784, "nsga2_search": 0.3434999999999988, "postprocessing": 0.19960000000000022, "total": 0.9086999999999996}, "distance_formula": "sqrt(sum(w*delta^2))", "weights": "Input weights divided by their sum", "normalization": "Frozen training minima and maxima; improvements beyond ideal have zero loss", "reference_score": "S_c = 1/(1+D); TOPSIS/ARAS actual utility is reported separately", "direct_cfd_solves": 0, "runtime_initialization_seconds": 26.995399999991058, "runtime_warm": false}</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>browser_runtime</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>{"platform": "emscripten", "python": "3.13.2", "numpy": "2.2.5", "pandas": "2.3.3", "scipy": "1.14.1", "sklearn": "1.7.0", "openpyxl": "3.1.5", "pyodide": "0.29.3", "source_sha256": {"mtpv_optimizer/__init__.py": "c5393d3218aca0011f762aefd1443bed0233cfea21e009e6328c0d66d7319bd6", "mtpv_optimizer/core.py": "6dc6a26eb7e57f0d51cdfc7f571ec891e27ec8263ca2e75cf128a3d97d31645b", "mtpv_optimizer/coupled.py": "a6869ea24416dc86fc2611f4511ae75dae03c2f2902c54dd3f8a36d388a48d80", "mtpv_optimizer/dat_parser.py": "059582ea4a4f64574b5ed5854ecba11a1bd4a699082a583dacc3c116b25a5fde", "mtpv_optimizer/doe.py": "cbd571d6f4d589f7c057e1cfacbae60c71809ee8be0dd7b11e29f4297e8fd90a", "mtpv_optimizer/domain.py": "5def038bde5d6422f462b721e910440dc5a00ae4f4059b0f31fd053c0071eb20", "mtpv_optimizer/general.py": "ce7980db1d46688aec71f0543e08b0c847720cc6d69be9e98c8939e8134b597c", "mtpv_optimizer/nsga2.py": "dfd8fcbacc8f121d4e130483a8cb4616989b034bd679ec0350dde6b11253609a", "mtpv_optimizer/presets.py": "19622217b24e6c5dbc6f3965f7d8e7b6740409e430af27e756222a8f7dcc2b30", "mtpv_optimizer/problem.py": "71200acc9ff03474b9f61206d365e1a9785008be3e6dc68fdd7fe9a06414a4bb", "mtpv_optimizer/workflow.py": "7e8a59f79de74aa8885500d5ee3de15397e26861e3ada7efe4f5bf70889f3e7f", "mtpv_optimizer/scientific.py": "09c669f57c4c51e5a01403be4f6becbb6b91bcc8ab7eee0c857ac4072e6f0611"}, "scope": "General numerical-table workflow; no Qt, no private research records.", "browser_adjustment": "Forest estimators run with n_jobs=1 in the browser."}</t>
         </is>
       </c>
     </row>
